--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118630827</v>
+        <v>118630829</v>
       </c>
       <c r="B7" t="n">
-        <v>56343</v>
+        <v>56401</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,41 +1300,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>102932</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118630829</v>
+        <v>118630825</v>
       </c>
       <c r="B8" t="n">
-        <v>56401</v>
+        <v>56343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,30 +1428,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102932</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118630825</v>
+        <v>118630831</v>
       </c>
       <c r="B8" t="n">
-        <v>56343</v>
+        <v>56635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>100065</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118630831</v>
+        <v>118630825</v>
       </c>
       <c r="B9" t="n">
-        <v>56635</v>
+        <v>56343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,16 +1560,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>100045</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118630829</v>
+        <v>118630827</v>
       </c>
       <c r="B7" t="n">
-        <v>56401</v>
+        <v>56343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,41 +1300,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102932</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118630825</v>
+        <v>118630829</v>
       </c>
       <c r="B9" t="n">
-        <v>56343</v>
+        <v>56401</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,30 +1556,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100045</v>
+        <v>102932</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118630831</v>
+        <v>118630829</v>
       </c>
       <c r="B8" t="n">
-        <v>56635</v>
+        <v>56401</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,30 +1428,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100065</v>
+        <v>102932</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118630829</v>
+        <v>118630831</v>
       </c>
       <c r="B9" t="n">
-        <v>56401</v>
+        <v>56635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,30 +1556,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102932</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118630827</v>
+        <v>118630831</v>
       </c>
       <c r="B7" t="n">
-        <v>56343</v>
+        <v>56635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,16 +1304,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>100065</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1326,15 +1326,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118630831</v>
+        <v>118630827</v>
       </c>
       <c r="B9" t="n">
-        <v>56635</v>
+        <v>56343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,16 +1560,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>100045</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1582,15 +1582,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1419,11 +1419,11 @@
         <v>118630825</v>
       </c>
       <c r="B8" t="n">
-        <v>56345</v>
+        <v>56410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1419,7 +1419,7 @@
         <v>118630825</v>
       </c>
       <c r="B8" t="n">
-        <v>56410</v>
+        <v>56418</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1547,11 +1547,11 @@
         <v>118630829</v>
       </c>
       <c r="B9" t="n">
-        <v>56403</v>
+        <v>56483</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1419,7 +1419,7 @@
         <v>118630825</v>
       </c>
       <c r="B8" t="n">
-        <v>56425</v>
+        <v>56430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>118630829</v>
       </c>
       <c r="B9" t="n">
-        <v>56483</v>
+        <v>56488</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1562,11 +1562,6 @@
       <c r="E9" t="n">
         <v>102932</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kricka</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Anas crecca</t>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>118630829</v>
       </c>
       <c r="B9" t="n">
-        <v>56488</v>
+        <v>56492</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,6 +1561,11 @@
       </c>
       <c r="E9" t="n">
         <v>102932</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>118630829</v>
       </c>
       <c r="B9" t="n">
-        <v>56492</v>
+        <v>56493</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>118630829</v>
       </c>
       <c r="B9" t="n">
-        <v>56493</v>
+        <v>56587</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112915562</v>
+        <v>118630831</v>
       </c>
       <c r="B6" t="n">
-        <v>55869</v>
+        <v>56637</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,25 +1180,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102932</v>
+        <v>100065</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1206,9 +1206,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1219,7 +1227,7 @@
         <v>639243</v>
       </c>
       <c r="R6" t="n">
-        <v>6521299</v>
+        <v>6521300</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1246,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,26 +1284,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118630831</v>
+        <v>118630825</v>
       </c>
       <c r="B7" t="n">
-        <v>56637</v>
+        <v>56430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1304,16 +1312,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1323,7 +1331,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1379,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,262 +1421,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>118630825</v>
-      </c>
-      <c r="B8" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100045</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Cygnus cygnus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Nynäs NR, Vretaskogens våtmark, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>639243</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6521300</v>
-      </c>
-      <c r="S8" t="n">
-        <v>100</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Bälinge</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>118630829</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56587</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>102932</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kricka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Anas crecca</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Nynäs NR, Vretaskogens våtmark, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>639243</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6521300</v>
-      </c>
-      <c r="S9" t="n">
-        <v>100</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Bälinge</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Markus Forsberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1422,6 +1422,127 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124857507</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Vretaskogens våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>639243</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kerstin Spjuth</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kerstin Spjuth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14041-2020 artfynd.xlsx
+++ b/artfynd/A 14041-2020 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>124857507</v>
       </c>
       <c r="B8" t="n">
-        <v>57532</v>
+        <v>57629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
